--- a/dist/xlsx/county-centers.xlsx
+++ b/dist/xlsx/county-centers.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G485"/>
+  <dimension ref="A1:I485"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,6 +421,12 @@
       <c r="G1" t="str">
         <v>source_id</v>
       </c>
+      <c r="H1" t="str">
+        <v>source_feature_id</v>
+      </c>
+      <c r="I1" t="str">
+        <v>source_name</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -444,6 +450,12 @@
       <c r="G2" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H2" t="str">
+        <v>143127</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Arāk</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -467,6 +479,12 @@
       <c r="G3" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H3" t="str">
+        <v>142744</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Āshtīān</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -490,6 +508,12 @@
       <c r="G4" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H4" t="str">
+        <v>113636</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Tafresh</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -513,6 +537,12 @@
       <c r="G5" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H5" t="str">
+        <v>127403</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Khomeyn</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -536,6 +566,12 @@
       <c r="G6" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H6" t="str">
+        <v>136399</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Delījān</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -559,6 +595,12 @@
       <c r="G7" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H7" t="str">
+        <v>116667</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Sāveh</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -582,6 +624,12 @@
       <c r="G8" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H8" t="str">
+        <v>142567</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Shāzand</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -605,6 +653,12 @@
       <c r="G9" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H9" t="str">
+        <v>125438</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Maḩallāt</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -628,6 +682,12 @@
       <c r="G10" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H10" t="str">
+        <v>142676</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Āstārā</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -651,6 +711,12 @@
       <c r="G11" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H11" t="str">
+        <v>142679</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Āstāneh-ye Ashrafīyeh</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -674,6 +740,12 @@
       <c r="G12" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H12" t="str">
+        <v>141679</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Bandar-e Anzalī</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -697,6 +769,12 @@
       <c r="G13" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H13" t="str">
+        <v>113343</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Hashtpar</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -720,6 +798,12 @@
       <c r="G14" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H14" t="str">
+        <v>118743</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Rasht</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -743,6 +827,12 @@
       <c r="G15" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H15" t="str">
+        <v>41151</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Pā’īn-e Bāzār-e Rūdbār</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -766,6 +856,12 @@
       <c r="G16" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H16" t="str">
+        <v>118191</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Rūdsar</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -789,6 +885,12 @@
       <c r="G17" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H17" t="str">
+        <v>113860</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Şowme‘eh Sarā</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -812,6 +914,12 @@
       <c r="G18" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H18" t="str">
+        <v>134441</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Fūman</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -835,6 +943,12 @@
       <c r="G19" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H19" t="str">
+        <v>143534</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Āmol</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -858,6 +972,12 @@
       <c r="G20" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H20" t="str">
+        <v>142363</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Bābol</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -881,6 +1001,12 @@
       <c r="G21" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H21" t="str">
+        <v>140918</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Behshahr</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -904,6 +1030,12 @@
       <c r="G22" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H22" t="str">
+        <v>112656</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Tonekābon</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -927,6 +1059,12 @@
       <c r="G23" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H23" t="str">
+        <v>117773</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Rāmsar</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -950,6 +1088,12 @@
       <c r="G24" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H24" t="str">
+        <v>116996</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Sari</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -973,6 +1117,12 @@
       <c r="G25" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H25" t="str">
+        <v>120936</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Pol-e Sefīd</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -996,6 +1146,12 @@
       <c r="G26" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H26" t="str">
+        <v>144616</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Ahar</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1019,6 +1175,12 @@
       <c r="G27" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H27" t="str">
+        <v>113646</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Tabriz</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1042,6 +1204,12 @@
       <c r="G28" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H28" t="str">
+        <v>117368</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Sarāb</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1065,6 +1233,12 @@
       <c r="G29" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H29" t="str">
+        <v>124877</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Marāgheh</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1088,6 +1262,12 @@
       <c r="G30" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H30" t="str">
+        <v>124862</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Marand</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1111,6 +1291,12 @@
       <c r="G31" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H31" t="str">
+        <v>121801</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Orūmīyeh</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1134,6 +1320,12 @@
       <c r="G32" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H32" t="str">
+        <v>121110</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Piranshahr</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1157,6 +1349,12 @@
       <c r="G33" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H33" t="str">
+        <v>126972</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Khūy</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1180,6 +1378,12 @@
       <c r="G34" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H34" t="str">
+        <v>117111</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Sardasht</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1203,6 +1407,12 @@
       <c r="G35" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H35" t="str">
+        <v>117656</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Salmās</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1226,6 +1436,12 @@
       <c r="G36" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H36" t="str">
+        <v>125205</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Maku</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1249,6 +1465,12 @@
       <c r="G37" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H37" t="str">
+        <v>125446</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Mahābād</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1272,6 +1494,12 @@
       <c r="G38" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H38" t="str">
+        <v>124085</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Mīāndoāb</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1295,6 +1523,12 @@
       <c r="G39" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H39" t="str">
+        <v>122698</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Naqadeh</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -1318,6 +1552,12 @@
       <c r="G40" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H40" t="str">
+        <v>135175</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Eslāmābād-e Gharb</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1341,6 +1581,12 @@
       <c r="G41" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H41" t="str">
+        <v>128226</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Kermanshah</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -1364,6 +1610,12 @@
       <c r="G42" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H42" t="str">
+        <v>121240</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Pāveh</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1387,6 +1639,12 @@
       <c r="G43" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H43" t="str">
+        <v>120931</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Sarpol-e Z̄ahāb</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1410,6 +1668,12 @@
       <c r="G44" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H44" t="str">
+        <v>114049</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Sonqor</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -1433,6 +1697,12 @@
       <c r="G45" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H45" t="str">
+        <v>119586</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Qaşr-e Shīrīn</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -1456,6 +1726,12 @@
       <c r="G46" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H46" t="str">
+        <v>128831</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Kangāvar</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -1479,6 +1755,12 @@
       <c r="G47" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H47" t="str">
+        <v>133345</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Gīlān-e Gharb</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -1502,6 +1784,12 @@
       <c r="G48" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H48" t="str">
+        <v>25883</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Javānrūd</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -1525,6 +1813,12 @@
       <c r="G49" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H49" t="str">
+        <v>145459</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Abadan</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -1548,6 +1842,12 @@
       <c r="G50" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H50" t="str">
+        <v>143420</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Andīmeshk</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -1571,6 +1871,12 @@
       <c r="G51" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H51" t="str">
+        <v>144448</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Ahvaz</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -1594,6 +1900,12 @@
       <c r="G52" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H52" t="str">
+        <v>130697</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Īz̄eh</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -1617,6 +1929,12 @@
       <c r="G53" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H53" t="str">
+        <v>141663</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Bandar-e Māhshahr</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -1640,6 +1958,12 @@
       <c r="G54" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H54" t="str">
+        <v>140951</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Behbahān</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -1663,6 +1987,12 @@
       <c r="G55" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H55" t="str">
+        <v>127319</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Khorramshahr</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -1686,6 +2016,12 @@
       <c r="G56" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H56" t="str">
+        <v>136256</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Dezful</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -1709,6 +2045,12 @@
       <c r="G57" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H57" t="str">
+        <v>137268</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Sūsangerd</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -1732,6 +2074,12 @@
       <c r="G58" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H58" t="str">
+        <v>145449</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Abadeh</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -1755,6 +2103,12 @@
       <c r="G59" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H59" t="str">
+        <v>135094</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Estahbān</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -1778,6 +2132,12 @@
       <c r="G60" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H60" t="str">
+        <v>135355</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Eqlīd</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -1801,6 +2161,12 @@
       <c r="G61" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H61" t="str">
+        <v>130531</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Jahrom</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -1824,6 +2190,12 @@
       <c r="G62" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H62" t="str">
+        <v>137956</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Dārāb</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -1847,6 +2219,12 @@
       <c r="G63" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H63" t="str">
+        <v>403656</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Ārdaḵān</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -1870,6 +2248,12 @@
       <c r="G64" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H64" t="str">
+        <v>115019</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Shiraz</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -1893,6 +2277,12 @@
       <c r="G65" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H65" t="str">
+        <v>134721</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Fasā</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -1916,6 +2306,12 @@
       <c r="G66" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H66" t="str">
+        <v>134518</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Fīrūzābād</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -1939,6 +2335,12 @@
       <c r="G67" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H67" t="str">
+        <v>142247</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Bāft</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -1962,6 +2364,12 @@
       <c r="G68" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H68" t="str">
+        <v>141736</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Bam</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -1985,6 +2393,12 @@
       <c r="G69" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H69" t="str">
+        <v>6925362</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Jīroft</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -2008,6 +2422,12 @@
       <c r="G70" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H70" t="str">
+        <v>118994</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Rafsanjān</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -2031,6 +2451,12 @@
       <c r="G71" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H71" t="str">
+        <v>111421</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Zarand</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -2054,6 +2480,12 @@
       <c r="G72" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H72" t="str">
+        <v>114259</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Sirjan</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -2077,6 +2509,12 @@
       <c r="G73" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H73" t="str">
+        <v>115781</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Shahr-e Bābak</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -2100,6 +2538,12 @@
       <c r="G74" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H74" t="str">
+        <v>128234</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Kerman</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -2123,6 +2567,12 @@
       <c r="G75" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H75" t="str">
+        <v>6961608</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Kahnūj</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -2146,6 +2596,12 @@
       <c r="G76" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H76" t="str">
+        <v>1159384</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Tāybād</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -2169,6 +2625,12 @@
       <c r="G77" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H77" t="str">
+        <v>112646</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Torbat-e Ḩeydarīyeh</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -2192,6 +2654,12 @@
       <c r="G78" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H78" t="str">
+        <v>1159362</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Torbat-e Jām</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -2215,6 +2683,12 @@
       <c r="G79" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H79" t="str">
+        <v>137585</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Dargaz</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -2238,6 +2712,12 @@
       <c r="G80" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H80" t="str">
+        <v>118063</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Sabzevar</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -2261,6 +2741,12 @@
       <c r="G81" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H81" t="str">
+        <v>143052</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Ardestān</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -2284,6 +2770,12 @@
       <c r="G82" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H82" t="str">
+        <v>418863</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Isfahan</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -2307,6 +2799,12 @@
       <c r="G83" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H83" t="str">
+        <v>418710</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Khomeynī Shahr</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -2330,6 +2828,12 @@
       <c r="G84" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H84" t="str">
+        <v>127033</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Khānsār</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -2353,6 +2857,12 @@
       <c r="G85" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H85" t="str">
+        <v>116406</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Semīrom</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -2376,6 +2886,12 @@
       <c r="G86" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H86" t="str">
+        <v>137929</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Dārān</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -2399,6 +2915,12 @@
       <c r="G87" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H87" t="str">
+        <v>134601</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Fereydūnshahr</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -2422,6 +2944,12 @@
       <c r="G88" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H88" t="str">
+        <v>418851</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Falāvarjān</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -2445,6 +2973,12 @@
       <c r="G89" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H89" t="str">
+        <v>418533</v>
+      </c>
+      <c r="I89" t="str">
+        <v>Shahreẕā</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -2468,6 +3002,12 @@
       <c r="G90" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H90" t="str">
+        <v>1160939</v>
+      </c>
+      <c r="I90" t="str">
+        <v>Iranshahr</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -2491,6 +3031,12 @@
       <c r="G91" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H91" t="str">
+        <v>1161724</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Chabahar</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -2514,6 +3060,12 @@
       <c r="G92" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H92" t="str">
+        <v>1160571</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Khāsh</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -2537,6 +3089,12 @@
       <c r="G93" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H93" t="str">
+        <v>1113217</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Zābol</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -2560,6 +3118,12 @@
       <c r="G94" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H94" t="str">
+        <v>1159301</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Zahedan</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -2583,6 +3147,12 @@
       <c r="G95" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H95" t="str">
+        <v>1159713</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Sarāvān</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -2606,6 +3176,12 @@
       <c r="G96" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H96" t="str">
+        <v>1160110</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Nīkshahr</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -2629,6 +3205,12 @@
       <c r="G97" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H97" t="str">
+        <v>1159836</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Rāsak</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -2652,6 +3234,12 @@
       <c r="G98" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H98" t="str">
+        <v>1160500</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Konārak</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -2675,6 +3263,12 @@
       <c r="G99" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H99" t="str">
+        <v>141584</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Bāneh</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -2698,6 +3292,12 @@
       <c r="G100" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H100" t="str">
+        <v>140521</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Bījār</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -2721,6 +3321,12 @@
       <c r="G101" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H101" t="str">
+        <v>117392</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Saqqez</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -2744,6 +3350,12 @@
       <c r="G102" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H102" t="str">
+        <v>117574</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Sanandaj</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -2767,6 +3379,12 @@
       <c r="G103" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H103" t="str">
+        <v>119161</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Qorveh</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -2790,6 +3408,12 @@
       <c r="G104" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H104" t="str">
+        <v>124778</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Marīvān</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -2813,6 +3437,12 @@
       <c r="G105" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H105" t="str">
+        <v>136156</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Dīvāndarreh</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106">
@@ -2836,6 +3466,12 @@
       <c r="G106" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H106" t="str">
+        <v>128905</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Kāmyārān</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107">
@@ -2859,6 +3495,12 @@
       <c r="G107" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H107" t="str">
+        <v>116739</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Sarvābād</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108">
@@ -2882,6 +3524,12 @@
       <c r="G108" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H108" t="str">
+        <v>112422</v>
+      </c>
+      <c r="I108" t="str">
+        <v>Tūyserkān</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109">
@@ -2905,6 +3553,12 @@
       <c r="G109" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H109" t="str">
+        <v>125185</v>
+      </c>
+      <c r="I109" t="str">
+        <v>Malāyer</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110">
@@ -2928,6 +3582,12 @@
       <c r="G110" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H110" t="str">
+        <v>122915</v>
+      </c>
+      <c r="I110" t="str">
+        <v>Nahāvand</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111">
@@ -2951,6 +3611,12 @@
       <c r="G111" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H111" t="str">
+        <v>132144</v>
+      </c>
+      <c r="I111" t="str">
+        <v>Hamadān</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112">
@@ -2974,6 +3640,12 @@
       <c r="G112" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H112" t="str">
+        <v>129904</v>
+      </c>
+      <c r="I112" t="str">
+        <v>Kabūdarāhang</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113">
@@ -2997,6 +3669,12 @@
       <c r="G113" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H113" t="str">
+        <v>142872</v>
+      </c>
+      <c r="I113" t="str">
+        <v>Asadābād</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114">
@@ -3020,6 +3698,12 @@
       <c r="G114" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H114" t="str">
+        <v>142000</v>
+      </c>
+      <c r="I114" t="str">
+        <v>Bahār</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115">
@@ -3043,6 +3727,12 @@
       <c r="G115" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H115" t="str">
+        <v>118681</v>
+      </c>
+      <c r="I115" t="str">
+        <v>Razan</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116">
@@ -3066,6 +3756,12 @@
       <c r="G116" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H116" t="str">
+        <v>134906</v>
+      </c>
+      <c r="I116" t="str">
+        <v>Fāmenīn</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117">
@@ -3089,6 +3785,12 @@
       <c r="G117" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H117" t="str">
+        <v>140046</v>
+      </c>
+      <c r="I117" t="str">
+        <v>Borūjen</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118">
@@ -3112,6 +3814,12 @@
       <c r="G118" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H118" t="str">
+        <v>115770</v>
+      </c>
+      <c r="I118" t="str">
+        <v>Shahr-e Kord</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119">
@@ -3135,6 +3843,12 @@
       <c r="G119" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H119" t="str">
+        <v>134762</v>
+      </c>
+      <c r="I119" t="str">
+        <v>Fārsān</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120">
@@ -3158,6 +3872,12 @@
       <c r="G120" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H120" t="str">
+        <v>125609</v>
+      </c>
+      <c r="I120" t="str">
+        <v>Lordegān</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121">
@@ -3181,6 +3901,12 @@
       <c r="G121" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H121" t="str">
+        <v>143070</v>
+      </c>
+      <c r="I121" t="str">
+        <v>Ardal</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122">
@@ -3204,6 +3930,12 @@
       <c r="G122" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H122" t="str">
+        <v>138799</v>
+      </c>
+      <c r="I122" t="str">
+        <v>Chelgard</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123">
@@ -3227,6 +3959,12 @@
       <c r="G123" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H123" t="str">
+        <v>115607</v>
+      </c>
+      <c r="I123" t="str">
+        <v>Shalamzār</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124">
@@ -3250,6 +3988,12 @@
       <c r="G124" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H124" t="str">
+        <v>117627</v>
+      </c>
+      <c r="I124" t="str">
+        <v>Sāmān</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125">
@@ -3273,6 +4017,12 @@
       <c r="G125" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H125" t="str">
+        <v>140891</v>
+      </c>
+      <c r="I125" t="str">
+        <v>Ben</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126">
@@ -3296,6 +4046,12 @@
       <c r="G126" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H126" t="str">
+        <v>143921</v>
+      </c>
+      <c r="I126" t="str">
+        <v>Alīgūdarz</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127">
@@ -3319,6 +4075,12 @@
       <c r="G127" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H127" t="str">
+        <v>140044</v>
+      </c>
+      <c r="I127" t="str">
+        <v>Borūjerd</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128">
@@ -3342,6 +4104,12 @@
       <c r="G128" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H128" t="str">
+        <v>127349</v>
+      </c>
+      <c r="I128" t="str">
+        <v>Khorramabad</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129">
@@ -3365,6 +4133,12 @@
       <c r="G129" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H129" t="str">
+        <v>24851</v>
+      </c>
+      <c r="I129" t="str">
+        <v>Nūrābād</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130">
@@ -3388,6 +4162,12 @@
       <c r="G130" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H130" t="str">
+        <v>135878</v>
+      </c>
+      <c r="I130" t="str">
+        <v>Dorūd</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131">
@@ -3411,6 +4191,12 @@
       <c r="G131" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H131" t="str">
+        <v>126409</v>
+      </c>
+      <c r="I131" t="str">
+        <v>Kūhdasht</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132">
@@ -3434,6 +4220,12 @@
       <c r="G132" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H132" t="str">
+        <v>142497</v>
+      </c>
+      <c r="I132" t="str">
+        <v>Aznā</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133">
@@ -3457,6 +4249,12 @@
       <c r="G133" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H133" t="str">
+        <v>120949</v>
+      </c>
+      <c r="I133" t="str">
+        <v>Poldokhtar</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134">
@@ -3480,6 +4278,12 @@
       <c r="G134" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H134" t="str">
+        <v>144269</v>
+      </c>
+      <c r="I134" t="str">
+        <v>Aleshtar</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135">
@@ -3503,6 +4307,12 @@
       <c r="G135" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H135" t="str">
+        <v>130802</v>
+      </c>
+      <c r="I135" t="str">
+        <v>Īlām</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136">
@@ -3526,6 +4336,12 @@
       <c r="G136" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H136" t="str">
+        <v>137436</v>
+      </c>
+      <c r="I136" t="str">
+        <v>Darreh Shahr</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137">
@@ -3549,6 +4365,12 @@
       <c r="G137" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H137" t="str">
+        <v>136702</v>
+      </c>
+      <c r="I137" t="str">
+        <v>Dehlorān</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138">
@@ -3572,6 +4394,12 @@
       <c r="G138" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H138" t="str">
+        <v>117304</v>
+      </c>
+      <c r="I138" t="str">
+        <v>Sarābleh</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139">
@@ -3595,6 +4423,12 @@
       <c r="G139" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H139" t="str">
+        <v>124291</v>
+      </c>
+      <c r="I139" t="str">
+        <v>Mehrān</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140">
@@ -3618,6 +4452,12 @@
       <c r="G140" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H140" t="str">
+        <v>145233</v>
+      </c>
+      <c r="I140" t="str">
+        <v>Ābdānān</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141">
@@ -3641,6 +4481,12 @@
       <c r="G141" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H141" t="str">
+        <v>129929</v>
+      </c>
+      <c r="I141" t="str">
+        <v>Eyvān</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142">
@@ -3664,6 +4510,12 @@
       <c r="G142" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H142" t="str">
+        <v>120539</v>
+      </c>
+      <c r="I142" t="str">
+        <v>Arkavaz</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143">
@@ -3687,6 +4539,12 @@
       <c r="G143" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H143" t="str">
+        <v>401555</v>
+      </c>
+      <c r="I143" t="str">
+        <v>Lūmār</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144">
@@ -3710,6 +4568,12 @@
       <c r="G144" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H144" t="str">
+        <v>66093</v>
+      </c>
+      <c r="I144" t="str">
+        <v>Yasuj</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145">
@@ -3733,6 +4597,12 @@
       <c r="G145" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H145" t="str">
+        <v>136987</v>
+      </c>
+      <c r="I145" t="str">
+        <v>Dehdasht</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146">
@@ -3756,6 +4626,12 @@
       <c r="G146" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H146" t="str">
+        <v>136014</v>
+      </c>
+      <c r="I146" t="str">
+        <v>Dogonbadan</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147">
@@ -3779,6 +4655,12 @@
       <c r="G147" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H147" t="str">
+        <v>137013</v>
+      </c>
+      <c r="I147" t="str">
+        <v>Sīsakht</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148">
@@ -3802,6 +4684,12 @@
       <c r="G148" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H148" t="str">
+        <v>125688</v>
+      </c>
+      <c r="I148" t="str">
+        <v>Līkak</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149">
@@ -3825,6 +4713,12 @@
       <c r="G149" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H149" t="str">
+        <v>138989</v>
+      </c>
+      <c r="I149" t="str">
+        <v>Charām</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150">
@@ -3848,6 +4742,12 @@
       <c r="G150" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H150" t="str">
+        <v>141124</v>
+      </c>
+      <c r="I150" t="str">
+        <v>Bāsht</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151">
@@ -3871,6 +4771,12 @@
       <c r="G151" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H151" t="str">
+        <v>125726</v>
+      </c>
+      <c r="I151" t="str">
+        <v>Landeh</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152">
@@ -3894,6 +4800,12 @@
       <c r="G152" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H152" t="str">
+        <v>124771</v>
+      </c>
+      <c r="I152" t="str">
+        <v>Mārgown</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153">
@@ -3917,6 +4829,12 @@
       <c r="G153" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H153" t="str">
+        <v>139817</v>
+      </c>
+      <c r="I153" t="str">
+        <v>Bushehr</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154">
@@ -3940,6 +4858,12 @@
       <c r="G154" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H154" t="str">
+        <v>144484</v>
+      </c>
+      <c r="I154" t="str">
+        <v>Ahram</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155">
@@ -3963,6 +4887,12 @@
       <c r="G155" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H155" t="str">
+        <v>140097</v>
+      </c>
+      <c r="I155" t="str">
+        <v>Borāzjān</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156">
@@ -3986,6 +4916,12 @@
       <c r="G156" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H156" t="str">
+        <v>127014</v>
+      </c>
+      <c r="I156" t="str">
+        <v>Khūrmūj</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157">
@@ -4009,6 +4945,12 @@
       <c r="G157" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H157" t="str">
+        <v>136280</v>
+      </c>
+      <c r="I157" t="str">
+        <v>Bandar-e Deyr</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158">
@@ -4024,13 +4966,19 @@
         <v>بندرکنگان</v>
       </c>
       <c r="E158">
-        <v>27.837</v>
+        <v>27.83434</v>
       </c>
       <c r="F158">
-        <v>52.062</v>
+        <v>52.06306</v>
       </c>
       <c r="G158" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H158" t="str">
+        <v>128847</v>
+      </c>
+      <c r="I158" t="str">
+        <v>Bandar-e Kangān</v>
       </c>
     </row>
     <row r="159">
@@ -4055,6 +5003,12 @@
       <c r="G159" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H159" t="str">
+        <v>134217</v>
+      </c>
+      <c r="I159" t="str">
+        <v>Bandar-e Genāveh</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160">
@@ -4078,6 +5032,12 @@
       <c r="G160" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H160" t="str">
+        <v>141676</v>
+      </c>
+      <c r="I160" t="str">
+        <v>Bandar-e Deylam</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161">
@@ -4101,6 +5061,12 @@
       <c r="G161" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H161" t="str">
+        <v>130451</v>
+      </c>
+      <c r="I161" t="str">
+        <v>Jam</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162">
@@ -4124,6 +5090,12 @@
       <c r="G162" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H162" t="str">
+        <v>145034</v>
+      </c>
+      <c r="I162" t="str">
+        <v>Abhar</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163">
@@ -4147,6 +5119,12 @@
       <c r="G163" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H163" t="str">
+        <v>6741193</v>
+      </c>
+      <c r="I163" t="str">
+        <v>Khodābandeh</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164">
@@ -4170,6 +5148,12 @@
       <c r="G164" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H164" t="str">
+        <v>111453</v>
+      </c>
+      <c r="I164" t="str">
+        <v>Zanjan</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165">
@@ -4193,6 +5177,12 @@
       <c r="G165" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H165" t="str">
+        <v>111246</v>
+      </c>
+      <c r="I165" t="str">
+        <v>Zarrīnābād</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166">
@@ -4216,6 +5206,12 @@
       <c r="G166" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H166" t="str">
+        <v>41210</v>
+      </c>
+      <c r="I166" t="str">
+        <v>Khorramdarreh</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167">
@@ -4239,6 +5235,12 @@
       <c r="G167" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H167" t="str">
+        <v>145407</v>
+      </c>
+      <c r="I167" t="str">
+        <v>Ābbar</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168">
@@ -4262,6 +5264,12 @@
       <c r="G168" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H168" t="str">
+        <v>125290</v>
+      </c>
+      <c r="I168" t="str">
+        <v>Māhneshān</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169">
@@ -4285,6 +5293,12 @@
       <c r="G169" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H169" t="str">
+        <v>138025</v>
+      </c>
+      <c r="I169" t="str">
+        <v>Dāmghān</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170">
@@ -4308,6 +5322,12 @@
       <c r="G170" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H170" t="str">
+        <v>116402</v>
+      </c>
+      <c r="I170" t="str">
+        <v>Semnan</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171">
@@ -4331,6 +5351,12 @@
       <c r="G171" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H171" t="str">
+        <v>135423</v>
+      </c>
+      <c r="I171" t="str">
+        <v>Shahrud</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172">
@@ -4354,6 +5380,12 @@
       <c r="G172" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H172" t="str">
+        <v>133964</v>
+      </c>
+      <c r="I172" t="str">
+        <v>Garmsār</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173">
@@ -4377,6 +5409,12 @@
       <c r="G173" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H173" t="str">
+        <v>7100777</v>
+      </c>
+      <c r="I173" t="str">
+        <v>Mahdishahr</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174">
@@ -4400,6 +5438,12 @@
       <c r="G174" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H174" t="str">
+        <v>143129</v>
+      </c>
+      <c r="I174" t="str">
+        <v>Ārādān</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175">
@@ -4423,6 +5467,12 @@
       <c r="G175" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H175" t="str">
+        <v>124562</v>
+      </c>
+      <c r="I175" t="str">
+        <v>Meyami</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176">
@@ -4446,6 +5496,12 @@
       <c r="G176" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H176" t="str">
+        <v>113952</v>
+      </c>
+      <c r="I176" t="str">
+        <v>Sorkheh</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177">
@@ -4469,6 +5525,12 @@
       <c r="G177" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H177" t="str">
+        <v>143073</v>
+      </c>
+      <c r="I177" t="str">
+        <v>Ardakān</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178">
@@ -4492,6 +5554,12 @@
       <c r="G178" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H178" t="str">
+        <v>142255</v>
+      </c>
+      <c r="I178" t="str">
+        <v>Bāfq</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179">
@@ -4515,6 +5583,12 @@
       <c r="G179" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H179" t="str">
+        <v>113632</v>
+      </c>
+      <c r="I179" t="str">
+        <v>Taft</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180">
@@ -4538,6 +5612,12 @@
       <c r="G180" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H180" t="str">
+        <v>124274</v>
+      </c>
+      <c r="I180" t="str">
+        <v>Mahrīz</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181">
@@ -4561,6 +5641,12 @@
       <c r="G181" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H181" t="str">
+        <v>111822</v>
+      </c>
+      <c r="I181" t="str">
+        <v>Yazd</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182">
@@ -4584,6 +5670,12 @@
       <c r="G182" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H182" t="str">
+        <v>124193</v>
+      </c>
+      <c r="I182" t="str">
+        <v>Meybod</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183">
@@ -4607,6 +5699,12 @@
       <c r="G183" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H183" t="str">
+        <v>145427</v>
+      </c>
+      <c r="I183" t="str">
+        <v>Abarkūh</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184">
@@ -4630,6 +5728,12 @@
       <c r="G184" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H184" t="str">
+        <v>66250</v>
+      </c>
+      <c r="I184" t="str">
+        <v>Ashkez̄ar</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185">
@@ -4653,6 +5757,12 @@
       <c r="G185" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H185" t="str">
+        <v>113556</v>
+      </c>
+      <c r="I185" t="str">
+        <v>Herāt</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186">
@@ -4668,13 +5778,19 @@
         <v>ابوموسی</v>
       </c>
       <c r="E186">
-        <v>25.864</v>
+        <v>25.875</v>
       </c>
       <c r="F186">
-        <v>55.023</v>
+        <v>55.03</v>
       </c>
       <c r="G186" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H186" t="str">
+        <v>292983</v>
+      </c>
+      <c r="I186" t="str">
+        <v>Abu Musa Island</v>
       </c>
     </row>
     <row r="187">
@@ -4699,6 +5815,12 @@
       <c r="G187" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H187" t="str">
+        <v>141681</v>
+      </c>
+      <c r="I187" t="str">
+        <v>Bandar Abbas</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188">
@@ -4722,6 +5844,12 @@
       <c r="G188" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H188" t="str">
+        <v>141665</v>
+      </c>
+      <c r="I188" t="str">
+        <v>Bandar-e Lengeh</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189">
@@ -4745,6 +5873,12 @@
       <c r="G189" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H189" t="str">
+        <v>119374</v>
+      </c>
+      <c r="I189" t="str">
+        <v>Qeshm</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190">
@@ -4768,6 +5902,12 @@
       <c r="G190" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H190" t="str">
+        <v>123941</v>
+      </c>
+      <c r="I190" t="str">
+        <v>Mīnāb</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191">
@@ -4783,13 +5923,19 @@
         <v>بندر جاسک</v>
       </c>
       <c r="E191">
-        <v>25.653</v>
+        <v>25.64533</v>
       </c>
       <c r="F191">
-        <v>57.775</v>
+        <v>57.77552</v>
       </c>
       <c r="G191" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H191" t="str">
+        <v>130276</v>
+      </c>
+      <c r="I191" t="str">
+        <v>Jask</v>
       </c>
     </row>
     <row r="192">
@@ -4814,6 +5960,12 @@
       <c r="G192" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H192" t="str">
+        <v>120351</v>
+      </c>
+      <c r="I192" t="str">
+        <v>Rūdān</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193">
@@ -4837,6 +5989,12 @@
       <c r="G193" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H193" t="str">
+        <v>132382</v>
+      </c>
+      <c r="I193" t="str">
+        <v>Ḩājjīābād</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194">
@@ -4860,6 +6018,12 @@
       <c r="G194" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H194" t="str">
+        <v>141104</v>
+      </c>
+      <c r="I194" t="str">
+        <v>Bastak</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195">
@@ -4883,6 +6047,12 @@
       <c r="G195" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H195" t="str">
+        <v>6683528</v>
+      </c>
+      <c r="I195" t="str">
+        <v>Tehrān</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196">
@@ -4906,6 +6076,12 @@
       <c r="G196" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H196" t="str">
+        <v>138042</v>
+      </c>
+      <c r="I196" t="str">
+        <v>Damāvand</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197">
@@ -4929,6 +6105,12 @@
       <c r="G197" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H197" t="str">
+        <v>9533872</v>
+      </c>
+      <c r="I197" t="str">
+        <v>Rey</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198">
@@ -4952,6 +6134,12 @@
       <c r="G198" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H198" t="str">
+        <v>113514</v>
+      </c>
+      <c r="I198" t="str">
+        <v>Tajrīsh</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199">
@@ -4975,6 +6163,12 @@
       <c r="G199" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H199" t="str">
+        <v>112214</v>
+      </c>
+      <c r="I199" t="str">
+        <v>Varāmīn</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200">
@@ -4998,6 +6192,12 @@
       <c r="G200" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H200" t="str">
+        <v>143860</v>
+      </c>
+      <c r="I200" t="str">
+        <v>Shahrīār</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201">
@@ -5021,6 +6221,12 @@
       <c r="G201" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H201" t="str">
+        <v>143083</v>
+      </c>
+      <c r="I201" t="str">
+        <v>Ardabīl</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202">
@@ -5044,6 +6250,12 @@
       <c r="G202" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H202" t="str">
+        <v>140494</v>
+      </c>
+      <c r="I202" t="str">
+        <v>Bīleh Savār</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203">
@@ -5067,6 +6279,12 @@
       <c r="G203" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H203" t="str">
+        <v>128008</v>
+      </c>
+      <c r="I203" t="str">
+        <v>Khalkhāl</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204">
@@ -5090,6 +6308,12 @@
       <c r="G204" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H204" t="str">
+        <v>124210</v>
+      </c>
+      <c r="I204" t="str">
+        <v>Meshgīn Shahr</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205">
@@ -5113,6 +6337,12 @@
       <c r="G205" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H205" t="str">
+        <v>133972</v>
+      </c>
+      <c r="I205" t="str">
+        <v>Germī</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206">
@@ -5136,6 +6366,12 @@
       <c r="G206" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H206" t="str">
+        <v>121380</v>
+      </c>
+      <c r="I206" t="str">
+        <v>Pārsābād</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207">
@@ -5159,6 +6395,12 @@
       <c r="G207" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H207" t="str">
+        <v>9514746</v>
+      </c>
+      <c r="I207" t="str">
+        <v>Gīvī</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208">
@@ -5182,6 +6424,12 @@
       <c r="G208" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H208" t="str">
+        <v>122721</v>
+      </c>
+      <c r="I208" t="str">
+        <v>Namīn</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209">
@@ -5205,6 +6453,12 @@
       <c r="G209" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H209" t="str">
+        <v>15269</v>
+      </c>
+      <c r="I209" t="str">
+        <v>Nīr</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210">
@@ -5228,6 +6482,12 @@
       <c r="G210" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H210" t="str">
+        <v>119208</v>
+      </c>
+      <c r="I210" t="str">
+        <v>Qom</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211">
@@ -5251,6 +6511,12 @@
       <c r="G211" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H211" t="str">
+        <v>133677</v>
+      </c>
+      <c r="I211" t="str">
+        <v>Ja‘farīyeh</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212">
@@ -5274,6 +6540,12 @@
       <c r="G212" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H212" t="str">
+        <v>122026</v>
+      </c>
+      <c r="I212" t="str">
+        <v>Kahak</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213">
@@ -5289,13 +6561,19 @@
         <v>بویین زهرا</v>
       </c>
       <c r="E213">
-        <v>35.766</v>
+        <v>35.7669</v>
       </c>
       <c r="F213">
-        <v>49.985</v>
+        <v>50.0578</v>
       </c>
       <c r="G213" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H213" t="str">
+        <v>139903</v>
+      </c>
+      <c r="I213" t="str">
+        <v>Bū’īn Zahrā</v>
       </c>
     </row>
     <row r="214">
@@ -5320,6 +6598,12 @@
       <c r="G214" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H214" t="str">
+        <v>113491</v>
+      </c>
+      <c r="I214" t="str">
+        <v>Tākestān</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215">
@@ -5343,6 +6627,12 @@
       <c r="G215" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H215" t="str">
+        <v>119505</v>
+      </c>
+      <c r="I215" t="str">
+        <v>Qazvin</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216">
@@ -5366,6 +6656,12 @@
       <c r="G216" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H216" t="str">
+        <v>144795</v>
+      </c>
+      <c r="I216" t="str">
+        <v>Ābyek</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217">
@@ -5389,6 +6685,12 @@
       <c r="G217" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H217" t="str">
+        <v>10570</v>
+      </c>
+      <c r="I217" t="str">
+        <v>Alvand</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218">
@@ -5412,6 +6714,12 @@
       <c r="G218" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H218" t="str">
+        <v>142642</v>
+      </c>
+      <c r="I218" t="str">
+        <v>Āvaj</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219">
@@ -5435,6 +6743,12 @@
       <c r="G219" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H219" t="str">
+        <v>141673</v>
+      </c>
+      <c r="I219" t="str">
+        <v>Bandar-e Gaz</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220">
@@ -5458,6 +6772,12 @@
       <c r="G220" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H220" t="str">
+        <v>141653</v>
+      </c>
+      <c r="I220" t="str">
+        <v>Bandar-e Torkaman</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221">
@@ -5481,6 +6801,12 @@
       <c r="G221" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H221" t="str">
+        <v>144038</v>
+      </c>
+      <c r="I221" t="str">
+        <v>'Alī Ābād-e Katūl</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222">
@@ -5504,6 +6830,12 @@
       <c r="G222" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H222" t="str">
+        <v>126572</v>
+      </c>
+      <c r="I222" t="str">
+        <v>Kord Kūy</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223">
@@ -5527,6 +6859,12 @@
       <c r="G223" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H223" t="str">
+        <v>132892</v>
+      </c>
+      <c r="I223" t="str">
+        <v>Gorgān</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224">
@@ -5550,6 +6888,12 @@
       <c r="G224" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H224" t="str">
+        <v>132938</v>
+      </c>
+      <c r="I224" t="str">
+        <v>Gonbad-e Kāvūs</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225">
@@ -5573,6 +6917,12 @@
       <c r="G225" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H225" t="str">
+        <v>123927</v>
+      </c>
+      <c r="I225" t="str">
+        <v>Mīnūdasht</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226">
@@ -5596,6 +6946,12 @@
       <c r="G226" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H226" t="str">
+        <v>7329809</v>
+      </c>
+      <c r="I226" t="str">
+        <v>Āq Qalā</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227">
@@ -5619,6 +6975,12 @@
       <c r="G227" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H227" t="str">
+        <v>129512</v>
+      </c>
+      <c r="I227" t="str">
+        <v>Kalāleh</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228">
@@ -5642,6 +7004,12 @@
       <c r="G228" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H228" t="str">
+        <v>135298</v>
+      </c>
+      <c r="I228" t="str">
+        <v>Esfarāyen</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229">
@@ -5665,6 +7033,12 @@
       <c r="G229" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H229" t="str">
+        <v>140380</v>
+      </c>
+      <c r="I229" t="str">
+        <v>Bojnūrd</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230">
@@ -5688,6 +7062,12 @@
       <c r="G230" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H230" t="str">
+        <v>130524</v>
+      </c>
+      <c r="I230" t="str">
+        <v>Jājarm</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231">
@@ -5711,6 +7091,12 @@
       <c r="G231" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H231" t="str">
+        <v>114930</v>
+      </c>
+      <c r="I231" t="str">
+        <v>Shīrvān</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232">
@@ -5734,6 +7120,12 @@
       <c r="G232" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H232" t="str">
+        <v>134745</v>
+      </c>
+      <c r="I232" t="str">
+        <v>Fārūj</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233">
@@ -5757,6 +7149,12 @@
       <c r="G233" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H233" t="str">
+        <v>142768</v>
+      </c>
+      <c r="I233" t="str">
+        <v>Āshkhāneh</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234">
@@ -5780,6 +7178,12 @@
       <c r="G234" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H234" t="str">
+        <v>133978</v>
+      </c>
+      <c r="I234" t="str">
+        <v>Garmeh</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235">
@@ -5803,6 +7207,12 @@
       <c r="G235" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H235" t="str">
+        <v>118694</v>
+      </c>
+      <c r="I235" t="str">
+        <v>Rāz</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236">
@@ -5826,6 +7236,12 @@
       <c r="G236" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H236" t="str">
+        <v>117916</v>
+      </c>
+      <c r="I236" t="str">
+        <v>Şafīābād</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237">
@@ -5849,6 +7265,12 @@
       <c r="G237" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H237" t="str">
+        <v>140463</v>
+      </c>
+      <c r="I237" t="str">
+        <v>Bīrjand</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238">
@@ -5872,6 +7294,12 @@
       <c r="G238" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H238" t="str">
+        <v>142862</v>
+      </c>
+      <c r="I238" t="str">
+        <v>Asadīyeh</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239">
@@ -5895,6 +7323,12 @@
       <c r="G239" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H239" t="str">
+        <v>117204</v>
+      </c>
+      <c r="I239" t="str">
+        <v>Sarbīsheh</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240">
@@ -5918,6 +7352,12 @@
       <c r="G240" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H240" t="str">
+        <v>120694</v>
+      </c>
+      <c r="I240" t="str">
+        <v>Qā’en</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241">
@@ -5941,6 +7381,12 @@
       <c r="G241" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H241" t="str">
+        <v>1160120</v>
+      </c>
+      <c r="I241" t="str">
+        <v>Nehbandān</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242">
@@ -5964,6 +7410,12 @@
       <c r="G242" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H242" t="str">
+        <v>117232</v>
+      </c>
+      <c r="I242" t="str">
+        <v>Sarāyān</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243">
@@ -5987,6 +7439,12 @@
       <c r="G243" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H243" t="str">
+        <v>134613</v>
+      </c>
+      <c r="I243" t="str">
+        <v>Ferdows</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244">
@@ -6010,6 +7468,12 @@
       <c r="G244" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H244" t="str">
+        <v>9480732</v>
+      </c>
+      <c r="I244" t="str">
+        <v>Boshrūyeh</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245">
@@ -6033,6 +7497,12 @@
       <c r="G245" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H245" t="str">
+        <v>1161048</v>
+      </c>
+      <c r="I245" t="str">
+        <v>Ḩājjīābād</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246">
@@ -6056,6 +7526,12 @@
       <c r="G246" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H246" t="str">
+        <v>128747</v>
+      </c>
+      <c r="I246" t="str">
+        <v>Karaj</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247">
@@ -6079,6 +7555,12 @@
       <c r="G247" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H247" t="str">
+        <v>131691</v>
+      </c>
+      <c r="I247" t="str">
+        <v>Hashtgerd</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248">
@@ -6102,6 +7584,12 @@
       <c r="G248" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H248" t="str">
+        <v>122438</v>
+      </c>
+      <c r="I248" t="str">
+        <v>Naz̧arābād</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249">
@@ -6125,6 +7613,12 @@
       <c r="G249" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H249" t="str">
+        <v>9904</v>
+      </c>
+      <c r="I249" t="str">
+        <v>Ţāleqān</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250">
@@ -6148,6 +7642,12 @@
       <c r="G250" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H250" t="str">
+        <v>135205</v>
+      </c>
+      <c r="I250" t="str">
+        <v>Eshtehārd</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251">
@@ -6171,6 +7671,12 @@
       <c r="G251" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H251" t="str">
+        <v>112179</v>
+      </c>
+      <c r="I251" t="str">
+        <v>Fardīs</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252">
@@ -6194,6 +7700,12 @@
       <c r="G252" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H252" t="str">
+        <v>41672</v>
+      </c>
+      <c r="I252" t="str">
+        <v>Chahārbāgh</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253">
@@ -6217,6 +7729,12 @@
       <c r="G253" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H253" t="str">
+        <v>6657461</v>
+      </c>
+      <c r="I253" t="str">
+        <v>Māmūnīyeh</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254">
@@ -6240,6 +7758,12 @@
       <c r="G254" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H254" t="str">
+        <v>126715</v>
+      </c>
+      <c r="I254" t="str">
+        <v>Komījān</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255">
@@ -6263,6 +7787,12 @@
       <c r="G255" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H255" t="str">
+        <v>127389</v>
+      </c>
+      <c r="I255" t="str">
+        <v>Khondāb</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256">
@@ -6286,6 +7816,12 @@
       <c r="G256" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H256" t="str">
+        <v>134788</v>
+      </c>
+      <c r="I256" t="str">
+        <v>Farmahīn</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257">
@@ -6309,6 +7845,12 @@
       <c r="G257" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H257" t="str">
+        <v>125897</v>
+      </c>
+      <c r="I257" t="str">
+        <v>Langarūd</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258">
@@ -6332,6 +7874,12 @@
       <c r="G258" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H258" t="str">
+        <v>126015</v>
+      </c>
+      <c r="I258" t="str">
+        <v>Lāhījān</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259">
@@ -6355,6 +7903,12 @@
       <c r="G259" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H259" t="str">
+        <v>116076</v>
+      </c>
+      <c r="I259" t="str">
+        <v>Shaft</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260">
@@ -6378,6 +7932,12 @@
       <c r="G260" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H260" t="str">
+        <v>143539</v>
+      </c>
+      <c r="I260" t="str">
+        <v>Amlash</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261">
@@ -6401,6 +7961,12 @@
       <c r="G261" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H261" t="str">
+        <v>118532</v>
+      </c>
+      <c r="I261" t="str">
+        <v>Reẕvānshahr</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262">
@@ -6424,6 +7990,12 @@
       <c r="G262" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H262" t="str">
+        <v>114489</v>
+      </c>
+      <c r="I262" t="str">
+        <v>Sīāhkal</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263">
@@ -6447,6 +8019,12 @@
       <c r="G263" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H263" t="str">
+        <v>141015</v>
+      </c>
+      <c r="I263" t="str">
+        <v>Māsāl</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264">
@@ -6470,6 +8048,12 @@
       <c r="G264" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H264" t="str">
+        <v>127415</v>
+      </c>
+      <c r="I264" t="str">
+        <v>Khomām</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265">
@@ -6485,13 +8069,19 @@
         <v>قایم شهر</v>
       </c>
       <c r="E265">
-        <v>36.463</v>
+        <v>36.46671</v>
       </c>
       <c r="F265">
-        <v>52.86</v>
+        <v>52.86762</v>
       </c>
       <c r="G265" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H265" t="str">
+        <v>120695</v>
+      </c>
+      <c r="I265" t="str">
+        <v>Qā’em Shahr</v>
       </c>
     </row>
     <row r="266">
@@ -6516,6 +8106,12 @@
       <c r="G266" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H266" t="str">
+        <v>113797</v>
+      </c>
+      <c r="I266" t="str">
+        <v>Nūr</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267">
@@ -6539,6 +8135,12 @@
       <c r="G267" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H267" t="str">
+        <v>121959</v>
+      </c>
+      <c r="I267" t="str">
+        <v>Nowshahr</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268">
@@ -6562,6 +8164,12 @@
       <c r="G268" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H268" t="str">
+        <v>142358</v>
+      </c>
+      <c r="I268" t="str">
+        <v>Bābolsar</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269">
@@ -6585,6 +8193,12 @@
       <c r="G269" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H269" t="str">
+        <v>125328</v>
+      </c>
+      <c r="I269" t="str">
+        <v>Maḩmūdābād</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270">
@@ -6608,6 +8222,12 @@
       <c r="G270" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H270" t="str">
+        <v>122397</v>
+      </c>
+      <c r="I270" t="str">
+        <v>Nekā</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271">
@@ -6631,6 +8251,12 @@
       <c r="G271" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H271" t="str">
+        <v>139223</v>
+      </c>
+      <c r="I271" t="str">
+        <v>Chālūs</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272">
@@ -6654,6 +8280,12 @@
       <c r="G272" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H272" t="str">
+        <v>129933</v>
+      </c>
+      <c r="I272" t="str">
+        <v>Jūybār</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273">
@@ -6677,6 +8309,12 @@
       <c r="G273" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H273" t="str">
+        <v>134255</v>
+      </c>
+      <c r="I273" t="str">
+        <v>Galūgāh</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274">
@@ -6700,6 +8338,12 @@
       <c r="G274" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H274" t="str">
+        <v>134602</v>
+      </c>
+      <c r="I274" t="str">
+        <v>Fereydūn Kenār</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275">
@@ -6723,6 +8367,12 @@
       <c r="G275" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H275" t="str">
+        <v>145303</v>
+      </c>
+      <c r="I275" t="str">
+        <v>'Abās Ābād</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276">
@@ -6746,6 +8396,12 @@
       <c r="G276" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H276" t="str">
+        <v>113760</v>
+      </c>
+      <c r="I276" t="str">
+        <v>Sūrak</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277">
@@ -6769,6 +8425,12 @@
       <c r="G277" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H277" t="str">
+        <v>126962</v>
+      </c>
+      <c r="I277" t="str">
+        <v>Kīā Kolā</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278">
@@ -6792,6 +8454,12 @@
       <c r="G278" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H278" t="str">
+        <v>115001</v>
+      </c>
+      <c r="I278" t="str">
+        <v>Shīr Gāh</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279">
@@ -6815,6 +8483,12 @@
       <c r="G279" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H279" t="str">
+        <v>8781</v>
+      </c>
+      <c r="I279" t="str">
+        <v>Kalārdasht</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280">
@@ -6838,6 +8512,12 @@
       <c r="G280" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H280" t="str">
+        <v>124082</v>
+      </c>
+      <c r="I280" t="str">
+        <v>Mīāneh</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281">
@@ -6861,6 +8541,12 @@
       <c r="G281" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H281" t="str">
+        <v>142554</v>
+      </c>
+      <c r="I281" t="str">
+        <v>Hashtrūd</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282">
@@ -6884,6 +8570,12 @@
       <c r="G282" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H282" t="str">
+        <v>140889</v>
+      </c>
+      <c r="I282" t="str">
+        <v>Bonāb</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283">
@@ -6907,6 +8599,12 @@
       <c r="G283" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H283" t="str">
+        <v>23290</v>
+      </c>
+      <c r="I283" t="str">
+        <v>Bostānābād</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284">
@@ -6930,6 +8628,12 @@
       <c r="G284" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H284" t="str">
+        <v>116126</v>
+      </c>
+      <c r="I284" t="str">
+        <v>Shabestar</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285">
@@ -6953,6 +8657,12 @@
       <c r="G285" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H285" t="str">
+        <v>129201</v>
+      </c>
+      <c r="I285" t="str">
+        <v>Kaleybar</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286">
@@ -6976,6 +8686,12 @@
       <c r="G286" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H286" t="str">
+        <v>131528</v>
+      </c>
+      <c r="I286" t="str">
+        <v>Herīs</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287">
@@ -6999,6 +8715,12 @@
       <c r="G287" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H287" t="str">
+        <v>130081</v>
+      </c>
+      <c r="I287" t="str">
+        <v>Julfa</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288">
@@ -7022,6 +8744,12 @@
       <c r="G288" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H288" t="str">
+        <v>125112</v>
+      </c>
+      <c r="I288" t="str">
+        <v>Malekān</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289">
@@ -7045,6 +8773,12 @@
       <c r="G289" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H289" t="str">
+        <v>6686970</v>
+      </c>
+      <c r="I289" t="str">
+        <v>Āz̄arshahr</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290">
@@ -7068,6 +8802,12 @@
       <c r="G290" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H290" t="str">
+        <v>121781</v>
+      </c>
+      <c r="I290" t="str">
+        <v>Oskū</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291">
@@ -7091,6 +8831,12 @@
       <c r="G291" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H291" t="str">
+        <v>22451</v>
+      </c>
+      <c r="I291" t="str">
+        <v>Qarah Āghāj</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292">
@@ -7114,6 +8860,12 @@
       <c r="G292" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H292" t="str">
+        <v>112121</v>
+      </c>
+      <c r="I292" t="str">
+        <v>Varazqān</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293">
@@ -7137,6 +8889,12 @@
       <c r="G293" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H293" t="str">
+        <v>144443</v>
+      </c>
+      <c r="I293" t="str">
+        <v>Ajab Shīr</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294">
@@ -7160,6 +8918,12 @@
       <c r="G294" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H294" t="str">
+        <v>127409</v>
+      </c>
+      <c r="I294" t="str">
+        <v>Khomārlū</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295">
@@ -7183,6 +8947,12 @@
       <c r="G295" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H295" t="str">
+        <v>130854</v>
+      </c>
+      <c r="I295" t="str">
+        <v>Hūrānd</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296">
@@ -7198,13 +8968,19 @@
         <v>لیلان</v>
       </c>
       <c r="E296">
-        <v>36.96</v>
+        <v>38.669</v>
       </c>
       <c r="F296">
-        <v>46.18</v>
+        <v>46.2113</v>
       </c>
       <c r="G296" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H296" t="str">
+        <v>125686</v>
+      </c>
+      <c r="I296" t="str">
+        <v>Līlāb</v>
       </c>
     </row>
     <row r="297">
@@ -7229,6 +9005,12 @@
       <c r="G297" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H297" t="str">
+        <v>112634</v>
+      </c>
+      <c r="I297" t="str">
+        <v>Torkamān</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298">
@@ -7252,6 +9034,12 @@
       <c r="G298" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H298" t="str">
+        <v>139889</v>
+      </c>
+      <c r="I298" t="str">
+        <v>Būkān</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299">
@@ -7275,6 +9063,12 @@
       <c r="G299" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H299" t="str">
+        <v>117793</v>
+      </c>
+      <c r="I299" t="str">
+        <v>Shāhīn Dezh</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300">
@@ -7298,6 +9092,12 @@
       <c r="G300" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H300" t="str">
+        <v>113508</v>
+      </c>
+      <c r="I300" t="str">
+        <v>Takāb</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301">
@@ -7321,6 +9121,12 @@
       <c r="G301" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H301" t="str">
+        <v>121795</v>
+      </c>
+      <c r="I301" t="str">
+        <v>Oshnavīyeh</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302">
@@ -7344,6 +9150,12 @@
       <c r="G302" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H302" t="str">
+        <v>116326</v>
+      </c>
+      <c r="I302" t="str">
+        <v>Seyah Cheshmeh</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303">
@@ -7367,6 +9179,12 @@
       <c r="G303" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H303" t="str">
+        <v>120954</v>
+      </c>
+      <c r="I303" t="str">
+        <v>Poldasht</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304">
@@ -7390,6 +9208,12 @@
       <c r="G304" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H304" t="str">
+        <v>119730</v>
+      </c>
+      <c r="I304" t="str">
+        <v>Qarah Ẕīā’ od Dīn</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305">
@@ -7413,6 +9237,12 @@
       <c r="G305" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H305" t="str">
+        <v>401118</v>
+      </c>
+      <c r="I305" t="str">
+        <v>Showţ</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306">
@@ -7428,13 +9258,19 @@
         <v>چهاربرج</v>
       </c>
       <c r="E306">
-        <v>36.465</v>
+        <v>36.44112</v>
       </c>
       <c r="F306">
-        <v>46.704</v>
+        <v>46.68879</v>
       </c>
       <c r="G306" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H306" t="str">
+        <v>117944</v>
+      </c>
+      <c r="I306" t="str">
+        <v>Şafākhāneh</v>
       </c>
     </row>
     <row r="307">
@@ -7459,6 +9295,12 @@
       <c r="G307" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H307" t="str">
+        <v>141190</v>
+      </c>
+      <c r="I307" t="str">
+        <v>Bārūq</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308">
@@ -7482,6 +9324,12 @@
       <c r="G308" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H308" t="str">
+        <v>3315</v>
+      </c>
+      <c r="I308" t="str">
+        <v>Mīrābād</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309">
@@ -7505,6 +9353,12 @@
       <c r="G309" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H309" t="str">
+        <v>117835</v>
+      </c>
+      <c r="I309" t="str">
+        <v>Şaḩneh</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310">
@@ -7528,6 +9382,12 @@
       <c r="G310" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H310" t="str">
+        <v>131962</v>
+      </c>
+      <c r="I310" t="str">
+        <v>Harsīn</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311">
@@ -7551,6 +9411,12 @@
       <c r="G311" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H311" t="str">
+        <v>6709138</v>
+      </c>
+      <c r="I311" t="str">
+        <v>Tāzehābād</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312">
@@ -7566,13 +9432,19 @@
         <v>کرند</v>
       </c>
       <c r="E312">
-        <v>34.328</v>
+        <v>34.2842</v>
       </c>
       <c r="F312">
-        <v>47.586</v>
+        <v>46.2423</v>
       </c>
       <c r="G312" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H312" t="str">
+        <v>128252</v>
+      </c>
+      <c r="I312" t="str">
+        <v>Kerend-e Gharb</v>
       </c>
     </row>
     <row r="313">
@@ -7597,6 +9469,12 @@
       <c r="G313" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H313" t="str">
+        <v>118705</v>
+      </c>
+      <c r="I313" t="str">
+        <v>Ravānsar</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314">
@@ -7620,6 +9498,12 @@
       <c r="G314" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H314" t="str">
+        <v>118826</v>
+      </c>
+      <c r="I314" t="str">
+        <v>Rāmhormoz</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315">
@@ -7643,6 +9527,12 @@
       <c r="G315" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H315" t="str">
+        <v>116102</v>
+      </c>
+      <c r="I315" t="str">
+        <v>Shādegān</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316">
@@ -7666,6 +9556,12 @@
       <c r="G316" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H316" t="str">
+        <v>114584</v>
+      </c>
+      <c r="I316" t="str">
+        <v>Shūshtar</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317">
@@ -7689,6 +9585,12 @@
       <c r="G317" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H317" t="str">
+        <v>124620</v>
+      </c>
+      <c r="I317" t="str">
+        <v>Masjed Soleymān</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318">
@@ -7712,6 +9614,12 @@
       <c r="G318" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H318" t="str">
+        <v>114593</v>
+      </c>
+      <c r="I318" t="str">
+        <v>Shūsh</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319">
@@ -7735,6 +9643,12 @@
       <c r="G319" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H319" t="str">
+        <v>142114</v>
+      </c>
+      <c r="I319" t="str">
+        <v>Bāgh-e Malek</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320">
@@ -7758,6 +9672,12 @@
       <c r="G320" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H320" t="str">
+        <v>121861</v>
+      </c>
+      <c r="I320" t="str">
+        <v>Omīdīyeh</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321">
@@ -7781,6 +9701,12 @@
       <c r="G321" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H321" t="str">
+        <v>125938</v>
+      </c>
+      <c r="I321" t="str">
+        <v>Lālī</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322">
@@ -7804,6 +9730,12 @@
       <c r="G322" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H322" t="str">
+        <v>131559</v>
+      </c>
+      <c r="I322" t="str">
+        <v>Hendījān</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323">
@@ -7827,6 +9759,12 @@
       <c r="G323" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H323" t="str">
+        <v>118805</v>
+      </c>
+      <c r="I323" t="str">
+        <v>Rāmshīr</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324">
@@ -7850,6 +9788,12 @@
       <c r="G324" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H324" t="str">
+        <v>133884</v>
+      </c>
+      <c r="I324" t="str">
+        <v>Gotvand</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325">
@@ -7873,6 +9817,12 @@
       <c r="G325" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H325" t="str">
+        <v>120499</v>
+      </c>
+      <c r="I325" t="str">
+        <v>Qal‘eh-ye Khvājeh</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326">
@@ -7896,6 +9846,12 @@
       <c r="G326" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H326" t="str">
+        <v>132428</v>
+      </c>
+      <c r="I326" t="str">
+        <v>Haftkel</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327">
@@ -7919,6 +9875,12 @@
       <c r="G327" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H327" t="str">
+        <v>130821</v>
+      </c>
+      <c r="I327" t="str">
+        <v>Hoveyzeh</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328">
@@ -7942,6 +9904,12 @@
       <c r="G328" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H328" t="str">
+        <v>123389</v>
+      </c>
+      <c r="I328" t="str">
+        <v>Mollās̄ānī</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329">
@@ -7965,6 +9933,12 @@
       <c r="G329" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H329" t="str">
+        <v>132105</v>
+      </c>
+      <c r="I329" t="str">
+        <v>Ḥamīdiyeh</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330">
@@ -7988,6 +9962,12 @@
       <c r="G330" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H330" t="str">
+        <v>144696</v>
+      </c>
+      <c r="I330" t="str">
+        <v>Aghajari</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331">
@@ -8003,13 +9983,19 @@
         <v>کوت عبداله</v>
       </c>
       <c r="E331">
-        <v>31.245</v>
+        <v>31.23917</v>
       </c>
       <c r="F331">
-        <v>48.657</v>
+        <v>48.65639</v>
       </c>
       <c r="G331" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H331" t="str">
+        <v>126082</v>
+      </c>
+      <c r="I331" t="str">
+        <v>Kūt-e ‘Abdollāh</v>
       </c>
     </row>
     <row r="332">
@@ -8034,6 +10020,12 @@
       <c r="G332" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H332" t="str">
+        <v>285</v>
+      </c>
+      <c r="I332" t="str">
+        <v>Boneh-ye ‘Alvān</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333">
@@ -8057,6 +10049,12 @@
       <c r="G333" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H333" t="str">
+        <v>136983</v>
+      </c>
+      <c r="I333" t="str">
+        <v>Dehdez</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334">
@@ -8080,6 +10078,12 @@
       <c r="G334" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H334" t="str">
+        <v>116318</v>
+      </c>
+      <c r="I334" t="str">
+        <v>Şeydūn</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335">
@@ -8103,6 +10107,12 @@
       <c r="G335" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H335" t="str">
+        <v>128321</v>
+      </c>
+      <c r="I335" t="str">
+        <v>Kāzerūn</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336">
@@ -8126,6 +10136,12 @@
       <c r="G336" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H336" t="str">
+        <v>125877</v>
+      </c>
+      <c r="I336" t="str">
+        <v>Lār</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337">
@@ -8149,6 +10165,12 @@
       <c r="G337" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H337" t="str">
+        <v>124721</v>
+      </c>
+      <c r="I337" t="str">
+        <v>Marvdasht</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338">
@@ -8172,6 +10194,12 @@
       <c r="G338" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H338" t="str">
+        <v>121925</v>
+      </c>
+      <c r="I338" t="str">
+        <v>Nūrābād</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339">
@@ -8195,6 +10223,12 @@
       <c r="G339" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H339" t="str">
+        <v>122289</v>
+      </c>
+      <c r="I339" t="str">
+        <v>Neyrīz</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340">
@@ -8218,6 +10252,12 @@
       <c r="G340" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H340" t="str">
+        <v>125926</v>
+      </c>
+      <c r="I340" t="str">
+        <v>Lamerd</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341">
@@ -8241,6 +10281,12 @@
       <c r="G341" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H341" t="str">
+        <v>113723</v>
+      </c>
+      <c r="I341" t="str">
+        <v>Surian</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342">
@@ -8264,6 +10310,12 @@
       <c r="G342" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H342" t="str">
+        <v>142958</v>
+      </c>
+      <c r="I342" t="str">
+        <v>Arsanjān</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343">
@@ -8287,6 +10339,12 @@
       <c r="G343" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H343" t="str">
+        <v>137025</v>
+      </c>
+      <c r="I343" t="str">
+        <v>Şafāshahr</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344">
@@ -8310,6 +10368,12 @@
       <c r="G344" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H344" t="str">
+        <v>132380</v>
+      </c>
+      <c r="I344" t="str">
+        <v>Ḩājjīābād</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345">
@@ -8333,6 +10397,12 @@
       <c r="G345" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H345" t="str">
+        <v>119264</v>
+      </c>
+      <c r="I345" t="str">
+        <v>Qīr</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346">
@@ -8356,6 +10426,12 @@
       <c r="G346" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H346" t="str">
+        <v>123485</v>
+      </c>
+      <c r="I346" t="str">
+        <v>Mohr</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347">
@@ -8379,6 +10455,12 @@
       <c r="G347" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H347" t="str">
+        <v>134781</v>
+      </c>
+      <c r="I347" t="str">
+        <v>Farrāshband</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348">
@@ -8402,6 +10484,12 @@
       <c r="G348" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H348" t="str">
+        <v>118123</v>
+      </c>
+      <c r="I348" t="str">
+        <v>Sa‘ādat Shahr</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349">
@@ -8425,6 +10513,12 @@
       <c r="G349" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H349" t="str">
+        <v>127382</v>
+      </c>
+      <c r="I349" t="str">
+        <v>Khonj</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350">
@@ -8448,6 +10542,12 @@
       <c r="G350" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H350" t="str">
+        <v>116725</v>
+      </c>
+      <c r="I350" t="str">
+        <v>Sarvestān</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351">
@@ -8471,6 +10571,12 @@
       <c r="G351" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H351" t="str">
+        <v>124622</v>
+      </c>
+      <c r="I351" t="str">
+        <v>Maşīrī</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352">
@@ -8494,6 +10600,12 @@
       <c r="G352" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H352" t="str">
+        <v>133595</v>
+      </c>
+      <c r="I352" t="str">
+        <v>Gerāsh</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353">
@@ -8517,6 +10629,12 @@
       <c r="G353" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H353" t="str">
+        <v>44439</v>
+      </c>
+      <c r="I353" t="str">
+        <v>Kavār</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354">
@@ -8540,6 +10658,12 @@
       <c r="G354" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H354" t="str">
+        <v>127613</v>
+      </c>
+      <c r="I354" t="str">
+        <v>Kherāmeh</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355">
@@ -8563,6 +10687,12 @@
       <c r="G355" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H355" t="str">
+        <v>111327</v>
+      </c>
+      <c r="I355" t="str">
+        <v>Zarqān</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356">
@@ -8586,6 +10716,12 @@
       <c r="G356" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H356" t="str">
+        <v>116364</v>
+      </c>
+      <c r="I356" t="str">
+        <v>Tall Beyẕā</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357">
@@ -8609,6 +10745,12 @@
       <c r="G357" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H357" t="str">
+        <v>131508</v>
+      </c>
+      <c r="I357" t="str">
+        <v>Ḩesāmī</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358">
@@ -8624,13 +10766,19 @@
         <v>قایمیه</v>
       </c>
       <c r="E358">
-        <v>29.846</v>
+        <v>29.61919</v>
       </c>
       <c r="F358">
-        <v>51.57</v>
+        <v>51.6535</v>
       </c>
       <c r="G358" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H358" t="str">
+        <v>128321</v>
+      </c>
+      <c r="I358" t="str">
+        <v>Kāzerūn</v>
       </c>
     </row>
     <row r="359">
@@ -8655,6 +10803,12 @@
       <c r="G359" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H359" t="str">
+        <v>142386</v>
+      </c>
+      <c r="I359" t="str">
+        <v>Bāb Anār</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360">
@@ -8678,6 +10832,12 @@
       <c r="G360" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H360" t="str">
+        <v>113090</v>
+      </c>
+      <c r="I360" t="str">
+        <v>Ābādeh Ţashk</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361">
@@ -8701,6 +10861,12 @@
       <c r="G361" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H361" t="str">
+        <v>135053</v>
+      </c>
+      <c r="I361" t="str">
+        <v>Evaz</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362">
@@ -8724,6 +10890,12 @@
       <c r="G362" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H362" t="str">
+        <v>129931</v>
+      </c>
+      <c r="I362" t="str">
+        <v>Jūyom</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363">
@@ -8747,6 +10919,12 @@
       <c r="G363" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H363" t="str">
+        <v>124647</v>
+      </c>
+      <c r="I363" t="str">
+        <v>Bardsīr</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364">
@@ -8770,6 +10948,12 @@
       <c r="G364" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H364" t="str">
+        <v>118704</v>
+      </c>
+      <c r="I364" t="str">
+        <v>Rāvar</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365">
@@ -8793,6 +10977,12 @@
       <c r="G365" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H365" t="str">
+        <v>143471</v>
+      </c>
+      <c r="I365" t="str">
+        <v>‘Anbarābād</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366">
@@ -8816,6 +11006,12 @@
       <c r="G366" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H366" t="str">
+        <v>124914</v>
+      </c>
+      <c r="I366" t="str">
+        <v>Manūjān</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367">
@@ -8839,6 +11035,12 @@
       <c r="G367" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H367" t="str">
+        <v>126411</v>
+      </c>
+      <c r="I367" t="str">
+        <v>Kūhbanān</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368">
@@ -8862,6 +11064,12 @@
       <c r="G368" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H368" t="str">
+        <v>6928551</v>
+      </c>
+      <c r="I368" t="str">
+        <v>Rūdbār</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369">
@@ -8885,6 +11093,12 @@
       <c r="G369" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H369" t="str">
+        <v>120323</v>
+      </c>
+      <c r="I369" t="str">
+        <v>Qal‘eh Ganj</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370">
@@ -8908,6 +11122,12 @@
       <c r="G370" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H370" t="str">
+        <v>123674</v>
+      </c>
+      <c r="I370" t="str">
+        <v>Moḩammadābād</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371">
@@ -8931,6 +11151,12 @@
       <c r="G371" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H371" t="str">
+        <v>119010</v>
+      </c>
+      <c r="I371" t="str">
+        <v>Rābor</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372">
@@ -8954,6 +11180,12 @@
       <c r="G372" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H372" t="str">
+        <v>134962</v>
+      </c>
+      <c r="I372" t="str">
+        <v>Fahraj</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373">
@@ -8977,6 +11209,12 @@
       <c r="G373" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H373" t="str">
+        <v>143499</v>
+      </c>
+      <c r="I373" t="str">
+        <v>Anār</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374">
@@ -9000,6 +11238,12 @@
       <c r="G374" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H374" t="str">
+        <v>118323</v>
+      </c>
+      <c r="I374" t="str">
+        <v>Narmāshīr</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375">
@@ -9023,6 +11267,12 @@
       <c r="G375" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H375" t="str">
+        <v>134735</v>
+      </c>
+      <c r="I375" t="str">
+        <v>Fāryāb</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376">
@@ -9038,13 +11288,19 @@
         <v>ارزوییه</v>
       </c>
       <c r="E376">
-        <v>28.44</v>
+        <v>28.45318</v>
       </c>
       <c r="F376">
-        <v>56.37</v>
+        <v>56.35994</v>
       </c>
       <c r="G376" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H376" t="str">
+        <v>142902</v>
+      </c>
+      <c r="I376" t="str">
+        <v>Orzū’īyeh</v>
       </c>
     </row>
     <row r="377">
@@ -9069,6 +11325,12 @@
       <c r="G377" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H377" t="str">
+        <v>46023</v>
+      </c>
+      <c r="I377" t="str">
+        <v>Ḩasanābād</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378">
@@ -9092,6 +11354,12 @@
       <c r="G378" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H378" t="str">
+        <v>7052385</v>
+      </c>
+      <c r="I378" t="str">
+        <v>Zeh-e Kalūt</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379">
@@ -9115,6 +11383,12 @@
       <c r="G379" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H379" t="str">
+        <v>119115</v>
+      </c>
+      <c r="I379" t="str">
+        <v>Qūchān</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380">
@@ -9138,6 +11412,12 @@
       <c r="G380" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H380" t="str">
+        <v>128447</v>
+      </c>
+      <c r="I380" t="str">
+        <v>Kāshmar</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381">
@@ -9161,6 +11441,12 @@
       <c r="G381" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H381" t="str">
+        <v>132961</v>
+      </c>
+      <c r="I381" t="str">
+        <v>Gonābād</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382">
@@ -9184,6 +11470,12 @@
       <c r="G382" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H382" t="str">
+        <v>124665</v>
+      </c>
+      <c r="I382" t="str">
+        <v>Mashhad</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383">
@@ -9207,6 +11499,12 @@
       <c r="G383" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H383" t="str">
+        <v>122285</v>
+      </c>
+      <c r="I383" t="str">
+        <v>Neyshābūr</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384">
@@ -9230,6 +11528,12 @@
       <c r="G384" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H384" t="str">
+        <v>138742</v>
+      </c>
+      <c r="I384" t="str">
+        <v>Chenārān</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385">
@@ -9253,6 +11557,12 @@
       <c r="G385" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H385" t="str">
+        <v>1160544</v>
+      </c>
+      <c r="I385" t="str">
+        <v>Khvāf</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386">
@@ -9276,6 +11586,12 @@
       <c r="G386" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H386" t="str">
+        <v>1159716</v>
+      </c>
+      <c r="I386" t="str">
+        <v>Sarakhs</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387">
@@ -9299,6 +11615,12 @@
       <c r="G387" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H387" t="str">
+        <v>134809</v>
+      </c>
+      <c r="I387" t="str">
+        <v>Farīmān</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388">
@@ -9322,6 +11644,12 @@
       <c r="G388" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H388" t="str">
+        <v>141349</v>
+      </c>
+      <c r="I388" t="str">
+        <v>Bardaskan</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389">
@@ -9345,6 +11673,12 @@
       <c r="G389" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H389" t="str">
+        <v>118328</v>
+      </c>
+      <c r="I389" t="str">
+        <v>Roshtkhvār</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390">
@@ -9368,6 +11702,12 @@
       <c r="G390" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H390" t="str">
+        <v>31265</v>
+      </c>
+      <c r="I390" t="str">
+        <v>Kalāt-e Nāderī</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391">
@@ -9391,6 +11731,12 @@
       <c r="G391" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H391" t="str">
+        <v>128025</v>
+      </c>
+      <c r="I391" t="str">
+        <v>Khalīlābād</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392">
@@ -9414,6 +11760,12 @@
       <c r="G392" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H392" t="str">
+        <v>134563</v>
+      </c>
+      <c r="I392" t="str">
+        <v>Feyẕābād</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393">
@@ -9437,6 +11789,12 @@
       <c r="G393" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H393" t="str">
+        <v>141891</v>
+      </c>
+      <c r="I393" t="str">
+        <v>Bajestān</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394">
@@ -9460,6 +11818,12 @@
       <c r="G394" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H394" t="str">
+        <v>112616</v>
+      </c>
+      <c r="I394" t="str">
+        <v>Ţorqabeh</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395">
@@ -9483,6 +11847,12 @@
       <c r="G395" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H395" t="str">
+        <v>31020</v>
+      </c>
+      <c r="I395" t="str">
+        <v>Fīrūzeh</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396">
@@ -9506,6 +11876,12 @@
       <c r="G396" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H396" t="str">
+        <v>130091</v>
+      </c>
+      <c r="I396" t="str">
+        <v>Joghtāy</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397">
@@ -9529,6 +11905,12 @@
       <c r="G397" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H397" t="str">
+        <v>135743</v>
+      </c>
+      <c r="I397" t="str">
+        <v>Dowlatābād</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398">
@@ -9552,6 +11934,12 @@
       <c r="G398" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H398" t="str">
+        <v>122375</v>
+      </c>
+      <c r="I398" t="str">
+        <v>Neqāb</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399">
@@ -9575,6 +11963,12 @@
       <c r="G399" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H399" t="str">
+        <v>1159905</v>
+      </c>
+      <c r="I399" t="str">
+        <v>Qal‘eh Now-e ‘Olyā</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400">
@@ -9598,6 +11992,12 @@
       <c r="G400" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H400" t="str">
+        <v>114105</v>
+      </c>
+      <c r="I400" t="str">
+        <v>Solţānābād</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401">
@@ -9621,6 +12021,12 @@
       <c r="G401" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H401" t="str">
+        <v>137125</v>
+      </c>
+      <c r="I401" t="str">
+        <v>Dāvarzan</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402">
@@ -9644,6 +12050,12 @@
       <c r="G402" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H402" t="str">
+        <v>7319</v>
+      </c>
+      <c r="I402" t="str">
+        <v>Şāleḩābād</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403">
@@ -9667,6 +12079,12 @@
       <c r="G403" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H403" t="str">
+        <v>118454</v>
+      </c>
+      <c r="I403" t="str">
+        <v>Rīvash</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404">
@@ -9690,6 +12108,12 @@
       <c r="G404" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H404" t="str">
+        <v>127129</v>
+      </c>
+      <c r="I404" t="str">
+        <v>Khowr</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405">
@@ -9713,6 +12137,12 @@
       <c r="G405" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H405" t="str">
+        <v>115226</v>
+      </c>
+      <c r="I405" t="str">
+        <v>Sheshtamad</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406">
@@ -9728,13 +12158,19 @@
         <v>گلبهار</v>
       </c>
       <c r="E406">
-        <v>36.52</v>
+        <v>36.56976</v>
       </c>
       <c r="F406">
-        <v>59.17</v>
+        <v>59.1904</v>
       </c>
       <c r="G406" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H406" t="str">
+        <v>7082152</v>
+      </c>
+      <c r="I406" t="str">
+        <v>Golbahār</v>
       </c>
     </row>
     <row r="407">
@@ -9759,6 +12195,12 @@
       <c r="G407" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H407" t="str">
+        <v>7341</v>
+      </c>
+      <c r="I407" t="str">
+        <v>‘Eshqābād</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408">
@@ -9782,6 +12224,12 @@
       <c r="G408" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H408" t="str">
+        <v>6861211</v>
+      </c>
+      <c r="I408" t="str">
+        <v>Kāshān</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409">
@@ -9805,6 +12253,12 @@
       <c r="G409" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H409" t="str">
+        <v>133037</v>
+      </c>
+      <c r="I409" t="str">
+        <v>Golpāyegān</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410">
@@ -9820,13 +12274,19 @@
         <v>زرین شهر</v>
       </c>
       <c r="E410">
-        <v>32.386</v>
+        <v>32.39057</v>
       </c>
       <c r="F410">
-        <v>51.377</v>
+        <v>51.37654</v>
       </c>
       <c r="G410" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H410" t="str">
+        <v>418418</v>
+      </c>
+      <c r="I410" t="str">
+        <v>Zarrīn Shahr</v>
       </c>
     </row>
     <row r="411">
@@ -9843,13 +12303,19 @@
         <v>نایین</v>
       </c>
       <c r="E411">
-        <v>32.86</v>
+        <v>32.86004</v>
       </c>
       <c r="F411">
-        <v>53.09</v>
+        <v>53.08693</v>
       </c>
       <c r="G411" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H411" t="str">
+        <v>122869</v>
+      </c>
+      <c r="I411" t="str">
+        <v>Nā’īn</v>
       </c>
     </row>
     <row r="412">
@@ -9874,6 +12340,12 @@
       <c r="G412" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H412" t="str">
+        <v>418606</v>
+      </c>
+      <c r="I412" t="str">
+        <v>Najafābād</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413">
@@ -9897,6 +12369,12 @@
       <c r="G413" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H413" t="str">
+        <v>122491</v>
+      </c>
+      <c r="I413" t="str">
+        <v>Naţanz</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414">
@@ -9920,6 +12398,12 @@
       <c r="G414" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H414" t="str">
+        <v>417472</v>
+      </c>
+      <c r="I414" t="str">
+        <v>Shāhīn Shahr</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415">
@@ -9943,6 +12427,12 @@
       <c r="G415" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H415" t="str">
+        <v>418625</v>
+      </c>
+      <c r="I415" t="str">
+        <v>Mobārakeh</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416">
@@ -9966,6 +12456,12 @@
       <c r="G416" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H416" t="str">
+        <v>143122</v>
+      </c>
+      <c r="I416" t="str">
+        <v>Ārān Bīdgol</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417">
@@ -9989,6 +12485,12 @@
       <c r="G417" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H417" t="str">
+        <v>418446</v>
+      </c>
+      <c r="I417" t="str">
+        <v>Tīrān</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418">
@@ -10012,6 +12514,12 @@
       <c r="G418" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H418" t="str">
+        <v>139780</v>
+      </c>
+      <c r="I418" t="str">
+        <v>Chādegān</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419">
@@ -10035,6 +12543,12 @@
       <c r="G419" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H419" t="str">
+        <v>137057</v>
+      </c>
+      <c r="I419" t="str">
+        <v>Dehāqān</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420">
@@ -10058,6 +12572,12 @@
       <c r="G420" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H420" t="str">
+        <v>418868</v>
+      </c>
+      <c r="I420" t="str">
+        <v>Dowlatābād</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421">
@@ -10081,6 +12601,12 @@
       <c r="G421" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H421" t="str">
+        <v>127029</v>
+      </c>
+      <c r="I421" t="str">
+        <v>Khūr</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422">
@@ -10096,13 +12622,19 @@
         <v>بویین و میاندشت</v>
       </c>
       <c r="E422">
-        <v>33.08</v>
+        <v>33.07612</v>
       </c>
       <c r="F422">
-        <v>50.15</v>
+        <v>50.16432</v>
       </c>
       <c r="G422" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H422" t="str">
+        <v>124101</v>
+      </c>
+      <c r="I422" t="str">
+        <v>Mīāndasht</v>
       </c>
     </row>
     <row r="423">
@@ -10127,6 +12659,12 @@
       <c r="G423" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H423" t="str">
+        <v>112535</v>
+      </c>
+      <c r="I423" t="str">
+        <v>Tūdeshk</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424">
@@ -10150,6 +12688,12 @@
       <c r="G424" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H424" t="str">
+        <v>6899676</v>
+      </c>
+      <c r="I424" t="str">
+        <v>Nīkābād</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425">
@@ -10173,6 +12717,12 @@
       <c r="G425" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H425" t="str">
+        <v>112124</v>
+      </c>
+      <c r="I425" t="str">
+        <v>Varzaneh</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426">
@@ -10196,6 +12746,12 @@
       <c r="G426" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H426" t="str">
+        <v>418806</v>
+      </c>
+      <c r="I426" t="str">
+        <v>Harand</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427">
@@ -10219,6 +12775,12 @@
       <c r="G427" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H427" t="str">
+        <v>1159302</v>
+      </c>
+      <c r="I427" t="str">
+        <v>Zehak</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428">
@@ -10242,6 +12804,12 @@
       <c r="G428" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H428" t="str">
+        <v>1161297</v>
+      </c>
+      <c r="I428" t="str">
+        <v>Dūst Moḩammad Khān</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429">
@@ -10265,6 +12833,12 @@
       <c r="G429" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H429" t="str">
+        <v>7102155</v>
+      </c>
+      <c r="I429" t="str">
+        <v>Galmūrtī</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430">
@@ -10288,6 +12862,12 @@
       <c r="G430" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H430" t="str">
+        <v>1159306</v>
+      </c>
+      <c r="I430" t="str">
+        <v>Mehrestān</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431">
@@ -10311,6 +12891,12 @@
       <c r="G431" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H431" t="str">
+        <v>1159431</v>
+      </c>
+      <c r="I431" t="str">
+        <v>Sūrān</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432">
@@ -10334,6 +12920,12 @@
       <c r="G432" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H432" t="str">
+        <v>1161887</v>
+      </c>
+      <c r="I432" t="str">
+        <v>Adīmī</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433">
@@ -10357,6 +12949,12 @@
       <c r="G433" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H433" t="str">
+        <v>1113006</v>
+      </c>
+      <c r="I433" t="str">
+        <v>Moḩammadābād</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434">
@@ -10380,6 +12978,12 @@
       <c r="G434" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H434" t="str">
+        <v>1160258</v>
+      </c>
+      <c r="I434" t="str">
+        <v>Mīrjāveh</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435">
@@ -10403,6 +13007,12 @@
       <c r="G435" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H435" t="str">
+        <v>1159884</v>
+      </c>
+      <c r="I435" t="str">
+        <v>Qaşr-e Qand</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436">
@@ -10426,6 +13036,12 @@
       <c r="G436" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H436" t="str">
+        <v>134894</v>
+      </c>
+      <c r="I436" t="str">
+        <v>Fannūj</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437">
@@ -10449,6 +13065,12 @@
       <c r="G437" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H437" t="str">
+        <v>1161735</v>
+      </c>
+      <c r="I437" t="str">
+        <v>Bampūr</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438">
@@ -10472,6 +13094,12 @@
       <c r="G438" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H438" t="str">
+        <v>1160088</v>
+      </c>
+      <c r="I438" t="str">
+        <v>Nūkābād</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439">
@@ -10495,6 +13123,12 @@
       <c r="G439" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H439" t="str">
+        <v>1160121</v>
+      </c>
+      <c r="I439" t="str">
+        <v>Negūr</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440">
@@ -10518,6 +13152,12 @@
       <c r="G440" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H440" t="str">
+        <v>1159709</v>
+      </c>
+      <c r="I440" t="str">
+        <v>Sarbāz</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441">
@@ -10533,13 +13173,19 @@
         <v>جالق</v>
       </c>
       <c r="E441">
-        <v>27.62</v>
+        <v>27.60287</v>
       </c>
       <c r="F441">
-        <v>61.23</v>
+        <v>62.71023</v>
       </c>
       <c r="G441" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H441" t="str">
+        <v>1160907</v>
+      </c>
+      <c r="I441" t="str">
+        <v>Jālq</v>
       </c>
     </row>
     <row r="442">
@@ -10564,6 +13210,12 @@
       <c r="G442" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H442" t="str">
+        <v>1161269</v>
+      </c>
+      <c r="I442" t="str">
+        <v>Espakeh</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443">
@@ -10587,6 +13239,12 @@
       <c r="G443" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H443" t="str">
+        <v>111431</v>
+      </c>
+      <c r="I443" t="str">
+        <v>Zarābād</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444">
@@ -10610,6 +13268,12 @@
       <c r="G444" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H444" t="str">
+        <v>136773</v>
+      </c>
+      <c r="I444" t="str">
+        <v>Dehgolān</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445">
@@ -10625,13 +13289,19 @@
         <v>قروه درگزین</v>
       </c>
       <c r="E445">
-        <v>35.313</v>
+        <v>35.30954</v>
       </c>
       <c r="F445">
-        <v>49.194</v>
+        <v>49.10023</v>
       </c>
       <c r="G445" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H445" t="str">
+        <v>119160</v>
+      </c>
+      <c r="I445" t="str">
+        <v>Qorveh-ye Dargazīn</v>
       </c>
     </row>
     <row r="446">
@@ -10656,6 +13326,12 @@
       <c r="G446" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H446" t="str">
+        <v>143758</v>
+      </c>
+      <c r="I446" t="str">
+        <v>Ālūnī</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447">
@@ -10679,6 +13355,12 @@
       <c r="G447" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H447" t="str">
+        <v>125077</v>
+      </c>
+      <c r="I447" t="str">
+        <v>Māl Khalīfeh</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448">
@@ -10694,13 +13376,19 @@
         <v>فرخ شهر</v>
       </c>
       <c r="E448">
-        <v>32.271</v>
+        <v>32.27174</v>
       </c>
       <c r="F448">
-        <v>50.98</v>
+        <v>50.98008</v>
       </c>
       <c r="G448" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H448" t="str">
+        <v>120678</v>
+      </c>
+      <c r="I448" t="str">
+        <v>Farrokh Shahr</v>
       </c>
     </row>
     <row r="449">
@@ -10725,6 +13413,12 @@
       <c r="G449" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H449" t="str">
+        <v>117345</v>
+      </c>
+      <c r="I449" t="str">
+        <v>Sarāb-e Dūreh</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450">
@@ -10748,6 +13442,12 @@
       <c r="G450" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H450" t="str">
+        <v>139015</v>
+      </c>
+      <c r="I450" t="str">
+        <v>Chaqābol</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451">
@@ -10771,6 +13471,12 @@
       <c r="G451" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H451" t="str">
+        <v>125016</v>
+      </c>
+      <c r="I451" t="str">
+        <v>Ma‘mūlān</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452">
@@ -10794,6 +13500,12 @@
       <c r="G452" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H452" t="str">
+        <v>415694</v>
+      </c>
+      <c r="I452" t="str">
+        <v>Badreh</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453">
@@ -10809,13 +13521,19 @@
         <v>توحید</v>
       </c>
       <c r="E453">
-        <v>33.7</v>
+        <v>27.82775</v>
       </c>
       <c r="F453">
-        <v>47.7</v>
+        <v>52.85789</v>
       </c>
       <c r="G453" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H453" t="str">
+        <v>8298952</v>
+      </c>
+      <c r="I453" t="str">
+        <v>Tohid</v>
       </c>
     </row>
     <row r="454">
@@ -10840,6 +13558,12 @@
       <c r="G454" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H454" t="str">
+        <v>138905</v>
+      </c>
+      <c r="I454" t="str">
+        <v>Chavār</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455">
@@ -10863,6 +13587,12 @@
       <c r="G455" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H455" t="str">
+        <v>142857</v>
+      </c>
+      <c r="I455" t="str">
+        <v>Bandar-e ‘Asalūyah</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456">
@@ -10878,13 +13608,19 @@
         <v>سلطانیه</v>
       </c>
       <c r="E456">
-        <v>36.434</v>
+        <v>36.43318</v>
       </c>
       <c r="F456">
-        <v>48.794</v>
+        <v>48.79471</v>
       </c>
       <c r="G456" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H456" t="str">
+        <v>117799</v>
+      </c>
+      <c r="I456" t="str">
+        <v>Solţānīyeh</v>
       </c>
     </row>
     <row r="457">
@@ -10909,6 +13645,12 @@
       <c r="G457" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H457" t="str">
+        <v>9533956</v>
+      </c>
+      <c r="I457" t="str">
+        <v>Bahābād</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458">
@@ -10932,6 +13674,12 @@
       <c r="G458" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H458" t="str">
+        <v>124724</v>
+      </c>
+      <c r="I458" t="str">
+        <v>Marvast</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459">
@@ -10955,6 +13703,12 @@
       <c r="G459" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H459" t="str">
+        <v>111407</v>
+      </c>
+      <c r="I459" t="str">
+        <v>Zārach</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460">
@@ -10970,13 +13724,19 @@
         <v>خمیر</v>
       </c>
       <c r="E460">
-        <v>26.95</v>
+        <v>26.9521</v>
       </c>
       <c r="F460">
-        <v>55.58</v>
+        <v>55.5851</v>
       </c>
       <c r="G460" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H460" t="str">
+        <v>127992</v>
+      </c>
+      <c r="I460" t="str">
+        <v>Bandar-e Khamīr</v>
       </c>
     </row>
     <row r="461">
@@ -11001,6 +13761,12 @@
       <c r="G461" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H461" t="str">
+        <v>112944</v>
+      </c>
+      <c r="I461" t="str">
+        <v>Tāzīān-e Pā’īn</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462">
@@ -11024,6 +13790,12 @@
       <c r="G462" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H462" t="str">
+        <v>114262</v>
+      </c>
+      <c r="I462" t="str">
+        <v>Sīrīk-e Kohneh</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463">
@@ -11047,6 +13819,12 @@
       <c r="G463" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H463" t="str">
+        <v>117116</v>
+      </c>
+      <c r="I463" t="str">
+        <v>Sardasht</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464">
@@ -11070,6 +13848,12 @@
       <c r="G464" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H464" t="str">
+        <v>449504</v>
+      </c>
+      <c r="I464" t="str">
+        <v>Eslamshahr</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465">
@@ -11093,6 +13877,12 @@
       <c r="G465" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H465" t="str">
+        <v>118367</v>
+      </c>
+      <c r="I465" t="str">
+        <v>Robāţ Karīm</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466">
@@ -11116,6 +13906,12 @@
       <c r="G466" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H466" t="str">
+        <v>9478811</v>
+      </c>
+      <c r="I466" t="str">
+        <v>Pākdasht</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467">
@@ -11139,6 +13935,12 @@
       <c r="G467" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H467" t="str">
+        <v>134462</v>
+      </c>
+      <c r="I467" t="str">
+        <v>Fīrūzkūh</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468">
@@ -11162,6 +13964,12 @@
       <c r="G468" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H468" t="str">
+        <v>120292</v>
+      </c>
+      <c r="I468" t="str">
+        <v>Qods</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469">
@@ -11185,6 +13993,12 @@
       <c r="G469" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H469" t="str">
+        <v>125188</v>
+      </c>
+      <c r="I469" t="str">
+        <v>Malārd</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470">
@@ -11208,6 +14022,12 @@
       <c r="G470" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H470" t="str">
+        <v>120972</v>
+      </c>
+      <c r="I470" t="str">
+        <v>Pīshvā</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471">
@@ -11231,6 +14051,12 @@
       <c r="G471" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H471" t="str">
+        <v>32900</v>
+      </c>
+      <c r="I471" t="str">
+        <v>Golestān</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472">
@@ -11254,6 +14080,12 @@
       <c r="G472" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H472" t="str">
+        <v>6681051</v>
+      </c>
+      <c r="I472" t="str">
+        <v>Pardīs</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473">
@@ -11277,6 +14109,12 @@
       <c r="G473" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H473" t="str">
+        <v>32767</v>
+      </c>
+      <c r="I473" t="str">
+        <v>Qarchak</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474">
@@ -11292,13 +14130,19 @@
         <v>سرعین</v>
       </c>
       <c r="E474">
-        <v>38.15</v>
+        <v>38.15022</v>
       </c>
       <c r="F474">
-        <v>48.08</v>
+        <v>48.07068</v>
       </c>
       <c r="G474" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H474" t="str">
+        <v>117048</v>
+      </c>
+      <c r="I474" t="str">
+        <v>Sara'eyn</v>
       </c>
     </row>
     <row r="475">
@@ -11323,6 +14167,12 @@
       <c r="G475" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H475" t="str">
+        <v>142703</v>
+      </c>
+      <c r="I475" t="str">
+        <v>Aşlān Dūz</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476">
@@ -11346,6 +14196,12 @@
       <c r="G476" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H476" t="str">
+        <v>16977</v>
+      </c>
+      <c r="I476" t="str">
+        <v>Angut</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477">
@@ -11369,6 +14225,12 @@
       <c r="G477" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H477" t="str">
+        <v>110831</v>
+      </c>
+      <c r="I477" t="str">
+        <v>Āzādshahr</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478">
@@ -11392,6 +14254,12 @@
       <c r="G478" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H478" t="str">
+        <v>118824</v>
+      </c>
+      <c r="I478" t="str">
+        <v>Rāmīān</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479">
@@ -11407,13 +14275,19 @@
         <v>مراوه</v>
       </c>
       <c r="E479">
-        <v>37.904</v>
+        <v>37.9041</v>
       </c>
       <c r="F479">
-        <v>55.96</v>
+        <v>55.95596</v>
       </c>
       <c r="G479" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H479" t="str">
+        <v>123295</v>
+      </c>
+      <c r="I479" t="str">
+        <v>Marāveh Tappeh</v>
       </c>
     </row>
     <row r="480">
@@ -11438,6 +14312,12 @@
       <c r="G480" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H480" t="str">
+        <v>40047</v>
+      </c>
+      <c r="I480" t="str">
+        <v>Gomīshān</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481">
@@ -11461,6 +14341,12 @@
       <c r="G481" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H481" t="str">
+        <v>134282</v>
+      </c>
+      <c r="I481" t="str">
+        <v>Gālīkesh</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482">
@@ -11484,6 +14370,12 @@
       <c r="G482" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H482" t="str">
+        <v>40788</v>
+      </c>
+      <c r="I482" t="str">
+        <v>Pīsh Qal‘eh</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483">
@@ -11507,6 +14399,12 @@
       <c r="G483" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H483" t="str">
+        <v>127098</v>
+      </c>
+      <c r="I483" t="str">
+        <v>Khūsf</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484">
@@ -11522,13 +14420,19 @@
         <v>طبس</v>
       </c>
       <c r="E484">
-        <v>33.595</v>
+        <v>33.59586</v>
       </c>
       <c r="F484">
-        <v>56.924</v>
+        <v>56.92437</v>
       </c>
       <c r="G484" t="str">
         <v>geonames-iran-2026-09-19</v>
+      </c>
+      <c r="H484" t="str">
+        <v>113659</v>
+      </c>
+      <c r="I484" t="str">
+        <v>Tabas</v>
       </c>
     </row>
     <row r="485">
@@ -11553,10 +14457,16 @@
       <c r="G485" t="str">
         <v>geonames-iran-2026-09-19</v>
       </c>
+      <c r="H485" t="str">
+        <v>135221</v>
+      </c>
+      <c r="I485" t="str">
+        <v>‘Eshqābād</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G485"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I485"/>
   </ignoredErrors>
 </worksheet>
 </file>